--- a/bills/JXZFSP01/-1003733706693/6d85008f7f7972fd90832a1022876df384976a1165aef80c1e3f256d2e720bdf/bill-current.xlsx
+++ b/bills/JXZFSP01/-1003733706693/6d85008f7f7972fd90832a1022876df384976a1165aef80c1e3f256d2e720bdf/bill-current.xlsx
@@ -75,12 +75,12 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>09/11 10:41:59</t>
+          <t>09/17 14:45:23</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>70000</t>
+          <t>150000</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -90,12 +90,12 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>8.4</t>
+          <t>8.35</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>8333.33</t>
+          <t>17964.07</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -199,86 +199,59 @@
         </is>
       </c>
     </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>09/11 12:03:55</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>8333</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>jxxiaomei521</t>
-        </is>
-      </c>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="13"/>
+    <row r="12"/>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>总计</t>
+        </is>
+      </c>
+    </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>总计</t>
+          <t>总入款</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>150000</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>总入款</t>
+          <t>应下发</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>70000</t>
+          <t>17964.07</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>应下发</t>
+          <t>已下发</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>8333.33</t>
+          <t>0</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>已下发</t>
+          <t>未下发</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>8333</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>未下发</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>0.33</t>
+          <t>17964.07</t>
         </is>
       </c>
     </row>

--- a/bills/JXZFSP01/-1003733706693/6d85008f7f7972fd90832a1022876df384976a1165aef80c1e3f256d2e720bdf/bill-current.xlsx
+++ b/bills/JXZFSP01/-1003733706693/6d85008f7f7972fd90832a1022876df384976a1165aef80c1e3f256d2e720bdf/bill-current.xlsx
@@ -199,59 +199,86 @@
         </is>
       </c>
     </row>
-    <row r="12"/>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>总计</t>
-        </is>
-      </c>
-    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>09/17 16:37:05</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>17964</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>jxxiaomei521</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="13"/>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>总入款</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>150000</t>
+          <t>总计</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>应下发</t>
+          <t>总入款</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>17964.07</t>
+          <t>150000</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>已下发</t>
+          <t>应下发</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>17964.07</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
+          <t>已下发</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>17964</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
           <t>未下发</t>
         </is>
       </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>17964.07</t>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>0.07</t>
         </is>
       </c>
     </row>

--- a/bills/JXZFSP01/-1003733706693/6d85008f7f7972fd90832a1022876df384976a1165aef80c1e3f256d2e720bdf/bill-current.xlsx
+++ b/bills/JXZFSP01/-1003733706693/6d85008f7f7972fd90832a1022876df384976a1165aef80c1e3f256d2e720bdf/bill-current.xlsx
@@ -75,12 +75,12 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>09/17 14:45:23</t>
+          <t>09/18 19:35:13</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>150000</t>
+          <t>320000</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -95,7 +95,7 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>17964.07</t>
+          <t>38323.35</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -105,7 +105,7 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>xinhui9</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -199,86 +199,59 @@
         </is>
       </c>
     </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>09/17 16:37:05</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>17964</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>jxxiaomei521</t>
-        </is>
-      </c>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="13"/>
+    <row r="12"/>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>总计</t>
+        </is>
+      </c>
+    </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>总计</t>
+          <t>总入款</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>320000</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>总入款</t>
+          <t>应下发</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>150000</t>
+          <t>38323.35</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>应下发</t>
+          <t>已下发</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>17964.07</t>
+          <t>0</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>已下发</t>
+          <t>未下发</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>17964</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>未下发</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>0.07</t>
+          <t>38323.35</t>
         </is>
       </c>
     </row>

--- a/bills/JXZFSP01/-1003733706693/6d85008f7f7972fd90832a1022876df384976a1165aef80c1e3f256d2e720bdf/bill-current.xlsx
+++ b/bills/JXZFSP01/-1003733706693/6d85008f7f7972fd90832a1022876df384976a1165aef80c1e3f256d2e720bdf/bill-current.xlsx
@@ -199,59 +199,86 @@
         </is>
       </c>
     </row>
-    <row r="12"/>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>总计</t>
-        </is>
-      </c>
-    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>09/18 21:26:48</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>38323</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>jxxiaomei521</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="13"/>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>总入款</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>320000</t>
+          <t>总计</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>应下发</t>
+          <t>总入款</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>38323.35</t>
+          <t>320000</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>已下发</t>
+          <t>应下发</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>38323.35</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
+          <t>已下发</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>38323</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
           <t>未下发</t>
         </is>
       </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>38323.35</t>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>0.35</t>
         </is>
       </c>
     </row>

--- a/bills/JXZFSP01/-1003733706693/6d85008f7f7972fd90832a1022876df384976a1165aef80c1e3f256d2e720bdf/bill-current.xlsx
+++ b/bills/JXZFSP01/-1003733706693/6d85008f7f7972fd90832a1022876df384976a1165aef80c1e3f256d2e720bdf/bill-current.xlsx
@@ -75,12 +75,12 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>09/18 19:35:13</t>
+          <t>09/21 14:33:05</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>320000</t>
+          <t>50000</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -90,12 +90,12 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>8.35</t>
+          <t>8.5</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>38323.35</t>
+          <t>5882.35</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -105,7 +105,7 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>xinhui9</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -199,86 +199,59 @@
         </is>
       </c>
     </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>09/18 21:26:48</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>38323</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>jxxiaomei521</t>
-        </is>
-      </c>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="13"/>
+    <row r="12"/>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>总计</t>
+        </is>
+      </c>
+    </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>总计</t>
+          <t>总入款</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>50000</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>总入款</t>
+          <t>应下发</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>320000</t>
+          <t>5882.35</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>应下发</t>
+          <t>已下发</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>38323.35</t>
+          <t>0</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>已下发</t>
+          <t>未下发</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>38323</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>未下发</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>0.35</t>
+          <t>5882.35</t>
         </is>
       </c>
     </row>

--- a/bills/JXZFSP01/-1003733706693/6d85008f7f7972fd90832a1022876df384976a1165aef80c1e3f256d2e720bdf/bill-current.xlsx
+++ b/bills/JXZFSP01/-1003733706693/6d85008f7f7972fd90832a1022876df384976a1165aef80c1e3f256d2e720bdf/bill-current.xlsx
@@ -199,59 +199,86 @@
         </is>
       </c>
     </row>
-    <row r="12"/>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>总计</t>
-        </is>
-      </c>
-    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>09/21 14:33:20</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>688</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>tiantiananxin</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="13"/>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>总入款</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>50000</t>
+          <t>总计</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>应下发</t>
+          <t>总入款</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>5882.35</t>
+          <t>50000</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>已下发</t>
+          <t>应下发</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>5882.35</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
+          <t>已下发</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>688</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
           <t>未下发</t>
         </is>
       </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>5882.35</t>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>5194.35</t>
         </is>
       </c>
     </row>

--- a/bills/JXZFSP01/-1003733706693/6d85008f7f7972fd90832a1022876df384976a1165aef80c1e3f256d2e720bdf/bill-current.xlsx
+++ b/bills/JXZFSP01/-1003733706693/6d85008f7f7972fd90832a1022876df384976a1165aef80c1e3f256d2e720bdf/bill-current.xlsx
@@ -202,83 +202,110 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
+          <t>09/21 15:43:17</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>5194</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>jxxiaomei521</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
           <t>09/21 14:33:20</t>
         </is>
       </c>
-      <c r="B12" t="inlineStr">
+      <c r="B13" t="inlineStr">
         <is>
           <t>688</t>
         </is>
       </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr">
+      <c r="C13" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
         <is>
           <t>tiantiananxin</t>
         </is>
       </c>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="13"/>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>总计</t>
-        </is>
-      </c>
-    </row>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="14"/>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>总入款</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>50000</t>
+          <t>总计</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>应下发</t>
+          <t>总入款</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>5882.35</t>
+          <t>50000</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>已下发</t>
+          <t>应下发</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>688</t>
+          <t>5882.35</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
+          <t>已下发</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>5882</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
           <t>未下发</t>
         </is>
       </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>5194.35</t>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>0.35</t>
         </is>
       </c>
     </row>

--- a/bills/JXZFSP01/-1003733706693/6d85008f7f7972fd90832a1022876df384976a1165aef80c1e3f256d2e720bdf/bill-current.xlsx
+++ b/bills/JXZFSP01/-1003733706693/6d85008f7f7972fd90832a1022876df384976a1165aef80c1e3f256d2e720bdf/bill-current.xlsx
@@ -75,12 +75,12 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>09/21 14:33:05</t>
+          <t>09/24 19:09:36</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>50000</t>
+          <t>610000</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -90,12 +90,12 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>8.5</t>
+          <t>8.6</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>5882.35</t>
+          <t>70930.23</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -105,7 +105,7 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>jxxiaomei521</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -199,113 +199,59 @@
         </is>
       </c>
     </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>09/21 15:43:17</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>5194</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>jxxiaomei521</t>
-        </is>
-      </c>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
+    <row r="12"/>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>09/21 14:33:20</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>688</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="D13" t="inlineStr">
-        <is>
-          <t>tiantiananxin</t>
-        </is>
-      </c>
-      <c r="E13" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="14"/>
+          <t>总计</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>总入款</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>610000</t>
+        </is>
+      </c>
+    </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>总计</t>
+          <t>应下发</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>70930.23</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>总入款</t>
+          <t>已下发</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>50000</t>
+          <t>0</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>应下发</t>
+          <t>未下发</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>5882.35</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>已下发</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>5882</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>未下发</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>0.35</t>
+          <t>70930.23</t>
         </is>
       </c>
     </row>

--- a/bills/JXZFSP01/-1003733706693/6d85008f7f7972fd90832a1022876df384976a1165aef80c1e3f256d2e720bdf/bill-current.xlsx
+++ b/bills/JXZFSP01/-1003733706693/6d85008f7f7972fd90832a1022876df384976a1165aef80c1e3f256d2e720bdf/bill-current.xlsx
@@ -75,7 +75,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>09/24 19:09:36</t>
+          <t>09/24 19:09:58</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -90,12 +90,12 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>8.6</t>
+          <t>8.3</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>70930.23</t>
+          <t>73493.98</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -227,7 +227,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>70930.23</t>
+          <t>73493.98</t>
         </is>
       </c>
     </row>
@@ -251,7 +251,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>70930.23</t>
+          <t>73493.98</t>
         </is>
       </c>
     </row>

--- a/bills/JXZFSP01/-1003733706693/6d85008f7f7972fd90832a1022876df384976a1165aef80c1e3f256d2e720bdf/bill-current.xlsx
+++ b/bills/JXZFSP01/-1003733706693/6d85008f7f7972fd90832a1022876df384976a1165aef80c1e3f256d2e720bdf/bill-current.xlsx
@@ -75,183 +75,225 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
+          <t>09/24 20:02:59</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>kefu111kf</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
           <t>09/24 19:09:58</t>
         </is>
       </c>
-      <c r="B5" t="inlineStr">
+      <c r="B6" t="inlineStr">
         <is>
           <t>610000</t>
         </is>
       </c>
-      <c r="C5" t="inlineStr">
+      <c r="C6" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
       </c>
-      <c r="D5" t="inlineStr">
+      <c r="D6" t="inlineStr">
         <is>
           <t>8.3</t>
         </is>
       </c>
-      <c r="E5" t="inlineStr">
+      <c r="E6" t="inlineStr">
         <is>
           <t>73493.98</t>
         </is>
       </c>
-      <c r="F5" t="inlineStr">
+      <c r="F6" t="inlineStr">
         <is>
           <t/>
         </is>
       </c>
-      <c r="G5" t="inlineStr">
+      <c r="G6" t="inlineStr">
         <is>
           <t>jxxiaomei521</t>
         </is>
       </c>
-      <c r="H5" t="inlineStr">
+      <c r="H6" t="inlineStr">
         <is>
           <t/>
         </is>
       </c>
     </row>
-    <row r="6"/>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>代付</t>
-        </is>
-      </c>
-    </row>
+    <row r="7"/>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
+          <t>代付</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
           <t>时间</t>
         </is>
       </c>
-      <c r="B8" t="inlineStr">
+      <c r="B9" t="inlineStr">
         <is>
           <t>金额</t>
         </is>
       </c>
-      <c r="C8" t="inlineStr">
+      <c r="C9" t="inlineStr">
         <is>
           <t>费率</t>
         </is>
       </c>
-      <c r="D8" t="inlineStr">
+      <c r="D9" t="inlineStr">
         <is>
           <t>汇率</t>
         </is>
       </c>
-      <c r="E8" t="inlineStr">
+      <c r="E9" t="inlineStr">
         <is>
           <t>结算</t>
         </is>
       </c>
-      <c r="F8" t="inlineStr">
+      <c r="F9" t="inlineStr">
         <is>
           <t>标记人</t>
         </is>
       </c>
-      <c r="G8" t="inlineStr">
+      <c r="G9" t="inlineStr">
         <is>
           <t>操作人</t>
         </is>
       </c>
-      <c r="H8" t="inlineStr">
+      <c r="H9" t="inlineStr">
         <is>
           <t>备注</t>
         </is>
       </c>
     </row>
-    <row r="9"/>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>下发</t>
-        </is>
-      </c>
-    </row>
+    <row r="10"/>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
+          <t>下发</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
           <t>时间</t>
         </is>
       </c>
-      <c r="B11" t="inlineStr">
+      <c r="B12" t="inlineStr">
         <is>
           <t>金额</t>
         </is>
       </c>
-      <c r="C11" t="inlineStr">
+      <c r="C12" t="inlineStr">
         <is>
           <t>标记人</t>
         </is>
       </c>
-      <c r="D11" t="inlineStr">
+      <c r="D12" t="inlineStr">
         <is>
           <t>操作人</t>
         </is>
       </c>
-      <c r="E11" t="inlineStr">
+      <c r="E12" t="inlineStr">
         <is>
           <t>备注</t>
         </is>
       </c>
     </row>
-    <row r="12"/>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>总计</t>
-        </is>
-      </c>
-    </row>
+    <row r="13"/>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>总入款</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>610000</t>
+          <t>总计</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>应下发</t>
+          <t>总入款</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>73493.98</t>
+          <t>610001</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>已下发</t>
+          <t>应下发</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>73494.98</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
+          <t>已下发</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
           <t>未下发</t>
         </is>
       </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>73493.98</t>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>73494.98</t>
         </is>
       </c>
     </row>

--- a/bills/JXZFSP01/-1003733706693/6d85008f7f7972fd90832a1022876df384976a1165aef80c1e3f256d2e720bdf/bill-current.xlsx
+++ b/bills/JXZFSP01/-1003733706693/6d85008f7f7972fd90832a1022876df384976a1165aef80c1e3f256d2e720bdf/bill-current.xlsx
@@ -72,144 +72,228 @@
         </is>
       </c>
     </row>
-    <row r="5"/>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>09/24 20:04:12</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>10000</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>8.25</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>1212.12</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>jxxiaomei521</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
+          <t>09/24 20:04:01</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>600000</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>8.25</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>72727.27</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>jxxiaomei521</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="7"/>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
           <t>代付</t>
         </is>
       </c>
     </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>时间</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>金额</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>费率</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>汇率</t>
-        </is>
-      </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>结算</t>
-        </is>
-      </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>标记人</t>
-        </is>
-      </c>
-      <c r="G7" t="inlineStr">
-        <is>
-          <t>操作人</t>
-        </is>
-      </c>
-      <c r="H7" t="inlineStr">
-        <is>
-          <t>备注</t>
-        </is>
-      </c>
-    </row>
-    <row r="8"/>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
+          <t>时间</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>金额</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>费率</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>汇率</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>结算</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>标记人</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>操作人</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>备注</t>
+        </is>
+      </c>
+    </row>
+    <row r="10"/>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
           <t>下发</t>
         </is>
       </c>
     </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>时间</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>金额</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>标记人</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>操作人</t>
-        </is>
-      </c>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>备注</t>
-        </is>
-      </c>
-    </row>
-    <row r="11"/>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>总计</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>总入款</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-    </row>
+          <t>时间</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>金额</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>标记人</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>操作人</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>备注</t>
+        </is>
+      </c>
+    </row>
+    <row r="13"/>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>应下发</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>0</t>
+          <t>总计</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>已下发</t>
+          <t>总入款</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>610000</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
+          <t>应下发</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>73939.39</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>已下发</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
           <t>未下发</t>
         </is>
       </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>0</t>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>73939.39</t>
         </is>
       </c>
     </row>

--- a/bills/JXZFSP01/-1003733706693/6d85008f7f7972fd90832a1022876df384976a1165aef80c1e3f256d2e720bdf/bill-current.xlsx
+++ b/bills/JXZFSP01/-1003733706693/6d85008f7f7972fd90832a1022876df384976a1165aef80c1e3f256d2e720bdf/bill-current.xlsx
@@ -241,59 +241,86 @@
         </is>
       </c>
     </row>
-    <row r="13"/>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>总计</t>
-        </is>
-      </c>
-    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>09/24 21:10:25</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>73939</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>jxxiaomei521</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="14"/>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>总入款</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>610000</t>
+          <t>总计</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>应下发</t>
+          <t>总入款</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>73939.39</t>
+          <t>610000</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>已下发</t>
+          <t>应下发</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>73939.39</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
+          <t>已下发</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>73939</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
           <t>未下发</t>
         </is>
       </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>73939.39</t>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>0.39</t>
         </is>
       </c>
     </row>

--- a/bills/JXZFSP01/-1003733706693/6d85008f7f7972fd90832a1022876df384976a1165aef80c1e3f256d2e720bdf/bill-current.xlsx
+++ b/bills/JXZFSP01/-1003733706693/6d85008f7f7972fd90832a1022876df384976a1165aef80c1e3f256d2e720bdf/bill-current.xlsx
@@ -75,12 +75,12 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>09/24 20:04:12</t>
+          <t>09/30 22:52:29</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>10000</t>
+          <t>150000</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -90,12 +90,12 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>8.25</t>
+          <t>8.5</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>1212.12</t>
+          <t>17647.06</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -105,7 +105,7 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>xinhui9</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -114,213 +114,144 @@
         </is>
       </c>
     </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>09/24 20:04:01</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>600000</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>8.25</t>
-        </is>
-      </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>72727.27</t>
-        </is>
-      </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t>jxxiaomei521</t>
-        </is>
-      </c>
-      <c r="H6" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="7"/>
+    <row r="6"/>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>代付</t>
+        </is>
+      </c>
+    </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>代付</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
           <t>时间</t>
         </is>
       </c>
-      <c r="B9" t="inlineStr">
+      <c r="B8" t="inlineStr">
         <is>
           <t>金额</t>
         </is>
       </c>
-      <c r="C9" t="inlineStr">
+      <c r="C8" t="inlineStr">
         <is>
           <t>费率</t>
         </is>
       </c>
-      <c r="D9" t="inlineStr">
+      <c r="D8" t="inlineStr">
         <is>
           <t>汇率</t>
         </is>
       </c>
-      <c r="E9" t="inlineStr">
+      <c r="E8" t="inlineStr">
         <is>
           <t>结算</t>
         </is>
       </c>
-      <c r="F9" t="inlineStr">
+      <c r="F8" t="inlineStr">
         <is>
           <t>标记人</t>
         </is>
       </c>
-      <c r="G9" t="inlineStr">
+      <c r="G8" t="inlineStr">
         <is>
           <t>操作人</t>
         </is>
       </c>
-      <c r="H9" t="inlineStr">
+      <c r="H8" t="inlineStr">
         <is>
           <t>备注</t>
         </is>
       </c>
     </row>
-    <row r="10"/>
+    <row r="9"/>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>下发</t>
+        </is>
+      </c>
+    </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>下发</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
           <t>时间</t>
         </is>
       </c>
-      <c r="B12" t="inlineStr">
+      <c r="B11" t="inlineStr">
         <is>
           <t>金额</t>
         </is>
       </c>
-      <c r="C12" t="inlineStr">
+      <c r="C11" t="inlineStr">
         <is>
           <t>标记人</t>
         </is>
       </c>
-      <c r="D12" t="inlineStr">
+      <c r="D11" t="inlineStr">
         <is>
           <t>操作人</t>
         </is>
       </c>
-      <c r="E12" t="inlineStr">
+      <c r="E11" t="inlineStr">
         <is>
           <t>备注</t>
         </is>
       </c>
     </row>
+    <row r="12"/>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>09/24 21:10:25</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>73939</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="D13" t="inlineStr">
-        <is>
-          <t>jxxiaomei521</t>
-        </is>
-      </c>
-      <c r="E13" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="14"/>
+          <t>总计</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>总入款</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>150000</t>
+        </is>
+      </c>
+    </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>总计</t>
+          <t>应下发</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>17647.06</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>总入款</t>
+          <t>已下发</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>610000</t>
+          <t>0</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>应下发</t>
+          <t>未下发</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>73939.39</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>已下发</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>73939</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>未下发</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>0.39</t>
+          <t>17647.06</t>
         </is>
       </c>
     </row>

--- a/bills/JXZFSP01/-1003733706693/6d85008f7f7972fd90832a1022876df384976a1165aef80c1e3f256d2e720bdf/bill-current.xlsx
+++ b/bills/JXZFSP01/-1003733706693/6d85008f7f7972fd90832a1022876df384976a1165aef80c1e3f256d2e720bdf/bill-current.xlsx
@@ -72,130 +72,115 @@
         </is>
       </c>
     </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>09/30 22:52:29</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>150000</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>8.5</t>
-        </is>
-      </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>17647.06</t>
-        </is>
-      </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>xinhui9</t>
-        </is>
-      </c>
-      <c r="H5" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="6"/>
+    <row r="5"/>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>代付</t>
+        </is>
+      </c>
+    </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>代付</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
           <t>时间</t>
         </is>
       </c>
-      <c r="B8" t="inlineStr">
+      <c r="B7" t="inlineStr">
         <is>
           <t>金额</t>
         </is>
       </c>
-      <c r="C8" t="inlineStr">
+      <c r="C7" t="inlineStr">
         <is>
           <t>费率</t>
         </is>
       </c>
-      <c r="D8" t="inlineStr">
+      <c r="D7" t="inlineStr">
         <is>
           <t>汇率</t>
         </is>
       </c>
-      <c r="E8" t="inlineStr">
+      <c r="E7" t="inlineStr">
         <is>
           <t>结算</t>
         </is>
       </c>
-      <c r="F8" t="inlineStr">
+      <c r="F7" t="inlineStr">
         <is>
           <t>标记人</t>
         </is>
       </c>
-      <c r="G8" t="inlineStr">
+      <c r="G7" t="inlineStr">
         <is>
           <t>操作人</t>
         </is>
       </c>
-      <c r="H8" t="inlineStr">
+      <c r="H7" t="inlineStr">
         <is>
           <t>备注</t>
         </is>
       </c>
     </row>
-    <row r="9"/>
+    <row r="8"/>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>下发</t>
+        </is>
+      </c>
+    </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>下发</t>
+          <t>时间</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>金额</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>标记人</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>操作人</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>备注</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>时间</t>
+          <t>10/01 00:00:27</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>金额</t>
+          <t>17647</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>标记人</t>
+          <t/>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>操作人</t>
+          <t>jxxiaomei521</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>备注</t>
+          <t/>
         </is>
       </c>
     </row>
@@ -215,7 +200,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>150000</t>
+          <t>0</t>
         </is>
       </c>
     </row>
@@ -227,7 +212,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>17647.06</t>
+          <t>0</t>
         </is>
       </c>
     </row>
@@ -239,7 +224,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>17647</t>
         </is>
       </c>
     </row>
@@ -251,7 +236,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>17647.06</t>
+          <t>-17647</t>
         </is>
       </c>
     </row>

--- a/bills/JXZFSP01/-1003733706693/6d85008f7f7972fd90832a1022876df384976a1165aef80c1e3f256d2e720bdf/bill-current.xlsx
+++ b/bills/JXZFSP01/-1003733706693/6d85008f7f7972fd90832a1022876df384976a1165aef80c1e3f256d2e720bdf/bill-current.xlsx
@@ -72,115 +72,130 @@
         </is>
       </c>
     </row>
-    <row r="5"/>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>代付</t>
-        </is>
-      </c>
-    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>10/17 11:22:50</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>100000</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>8.5</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>11764.71</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>xinhui9</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="6"/>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
+          <t>代付</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
           <t>时间</t>
         </is>
       </c>
-      <c r="B7" t="inlineStr">
+      <c r="B8" t="inlineStr">
         <is>
           <t>金额</t>
         </is>
       </c>
-      <c r="C7" t="inlineStr">
+      <c r="C8" t="inlineStr">
         <is>
           <t>费率</t>
         </is>
       </c>
-      <c r="D7" t="inlineStr">
+      <c r="D8" t="inlineStr">
         <is>
           <t>汇率</t>
         </is>
       </c>
-      <c r="E7" t="inlineStr">
+      <c r="E8" t="inlineStr">
         <is>
           <t>结算</t>
         </is>
       </c>
-      <c r="F7" t="inlineStr">
+      <c r="F8" t="inlineStr">
         <is>
           <t>标记人</t>
         </is>
       </c>
-      <c r="G7" t="inlineStr">
+      <c r="G8" t="inlineStr">
         <is>
           <t>操作人</t>
         </is>
       </c>
-      <c r="H7" t="inlineStr">
+      <c r="H8" t="inlineStr">
         <is>
           <t>备注</t>
         </is>
       </c>
     </row>
-    <row r="8"/>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>下发</t>
-        </is>
-      </c>
-    </row>
+    <row r="9"/>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>时间</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>金额</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>标记人</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>操作人</t>
-        </is>
-      </c>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>备注</t>
+          <t>下发</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>10/01 00:00:27</t>
+          <t>时间</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>17647</t>
+          <t>金额</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t/>
+          <t>标记人</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>操作人</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t/>
+          <t>备注</t>
         </is>
       </c>
     </row>
@@ -200,7 +215,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>100000</t>
         </is>
       </c>
     </row>
@@ -212,7 +227,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>11764.71</t>
         </is>
       </c>
     </row>
@@ -224,7 +239,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>17647</t>
+          <t>0</t>
         </is>
       </c>
     </row>
@@ -236,7 +251,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>-17647</t>
+          <t>11764.71</t>
         </is>
       </c>
     </row>

--- a/bills/JXZFSP01/-1003733706693/6d85008f7f7972fd90832a1022876df384976a1165aef80c1e3f256d2e720bdf/bill-current.xlsx
+++ b/bills/JXZFSP01/-1003733706693/6d85008f7f7972fd90832a1022876df384976a1165aef80c1e3f256d2e720bdf/bill-current.xlsx
@@ -199,59 +199,86 @@
         </is>
       </c>
     </row>
-    <row r="12"/>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>总计</t>
-        </is>
-      </c>
-    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>10/17 12:34:59</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>11764</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>jxxiaomei521</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="13"/>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>总入款</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>100000</t>
+          <t>总计</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>应下发</t>
+          <t>总入款</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>11764.71</t>
+          <t>100000</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>已下发</t>
+          <t>应下发</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>11764.71</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
+          <t>已下发</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>11764</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
           <t>未下发</t>
         </is>
       </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>11764.71</t>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>0.71</t>
         </is>
       </c>
     </row>

--- a/bills/JXZFSP01/-1003733706693/6d85008f7f7972fd90832a1022876df384976a1165aef80c1e3f256d2e720bdf/bill-current.xlsx
+++ b/bills/JXZFSP01/-1003733706693/6d85008f7f7972fd90832a1022876df384976a1165aef80c1e3f256d2e720bdf/bill-current.xlsx
@@ -75,7 +75,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>10/17 11:22:50</t>
+          <t>10/20 16:11:58</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -90,12 +90,12 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>8.5</t>
+          <t>8.3</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>11764.71</t>
+          <t>12048.19</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -199,86 +199,59 @@
         </is>
       </c>
     </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>10/17 12:34:59</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>11764</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>jxxiaomei521</t>
-        </is>
-      </c>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="13"/>
+    <row r="12"/>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>总计</t>
+        </is>
+      </c>
+    </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>总计</t>
+          <t>总入款</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>100000</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>总入款</t>
+          <t>应下发</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>100000</t>
+          <t>12048.19</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>应下发</t>
+          <t>已下发</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>11764.71</t>
+          <t>0</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>已下发</t>
+          <t>未下发</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>11764</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>未下发</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>0.71</t>
+          <t>12048.19</t>
         </is>
       </c>
     </row>

--- a/bills/JXZFSP01/-1003733706693/6d85008f7f7972fd90832a1022876df384976a1165aef80c1e3f256d2e720bdf/bill-current.xlsx
+++ b/bills/JXZFSP01/-1003733706693/6d85008f7f7972fd90832a1022876df384976a1165aef80c1e3f256d2e720bdf/bill-current.xlsx
@@ -199,59 +199,86 @@
         </is>
       </c>
     </row>
-    <row r="12"/>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>总计</t>
-        </is>
-      </c>
-    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>10/20 17:14:32</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>12048</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>jxxiaomei521</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="13"/>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>总入款</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>100000</t>
+          <t>总计</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>应下发</t>
+          <t>总入款</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>12048.19</t>
+          <t>100000</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>已下发</t>
+          <t>应下发</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>12048.19</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
+          <t>已下发</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>12048</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
           <t>未下发</t>
         </is>
       </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>12048.19</t>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>0.19</t>
         </is>
       </c>
     </row>

--- a/bills/JXZFSP01/-1003733706693/6d85008f7f7972fd90832a1022876df384976a1165aef80c1e3f256d2e720bdf/bill-current.xlsx
+++ b/bills/JXZFSP01/-1003733706693/6d85008f7f7972fd90832a1022876df384976a1165aef80c1e3f256d2e720bdf/bill-current.xlsx
@@ -75,12 +75,12 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>10/20 16:11:58</t>
+          <t>10/23 10:37:09</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>100000</t>
+          <t>50000</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -90,12 +90,12 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>8.3</t>
+          <t>8.4</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>12048.19</t>
+          <t>5952.38</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -105,7 +105,7 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>xinhui9</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -199,86 +199,59 @@
         </is>
       </c>
     </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>10/20 17:14:32</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>12048</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>jxxiaomei521</t>
-        </is>
-      </c>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="13"/>
+    <row r="12"/>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>总计</t>
+        </is>
+      </c>
+    </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>总计</t>
+          <t>总入款</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>50000</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>总入款</t>
+          <t>应下发</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>100000</t>
+          <t>5952.38</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>应下发</t>
+          <t>已下发</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>12048.19</t>
+          <t>0</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>已下发</t>
+          <t>未下发</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>12048</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>未下发</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>0.19</t>
+          <t>5952.38</t>
         </is>
       </c>
     </row>

--- a/bills/JXZFSP01/-1003733706693/6d85008f7f7972fd90832a1022876df384976a1165aef80c1e3f256d2e720bdf/bill-current.xlsx
+++ b/bills/JXZFSP01/-1003733706693/6d85008f7f7972fd90832a1022876df384976a1165aef80c1e3f256d2e720bdf/bill-current.xlsx
@@ -199,59 +199,86 @@
         </is>
       </c>
     </row>
-    <row r="12"/>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>总计</t>
-        </is>
-      </c>
-    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>10/23 10:38:04</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>228</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>tiantiananxin</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="13"/>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>总入款</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>50000</t>
+          <t>总计</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>应下发</t>
+          <t>总入款</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>5952.38</t>
+          <t>50000</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>已下发</t>
+          <t>应下发</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>5952.38</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
+          <t>已下发</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>228</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
           <t>未下发</t>
         </is>
       </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>5952.38</t>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>5724.38</t>
         </is>
       </c>
     </row>

--- a/bills/JXZFSP01/-1003733706693/6d85008f7f7972fd90832a1022876df384976a1165aef80c1e3f256d2e720bdf/bill-current.xlsx
+++ b/bills/JXZFSP01/-1003733706693/6d85008f7f7972fd90832a1022876df384976a1165aef80c1e3f256d2e720bdf/bill-current.xlsx
@@ -202,83 +202,110 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
+          <t>10/23 13:39:54</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>5724</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>jxxiaomei521</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
           <t>10/23 10:38:04</t>
         </is>
       </c>
-      <c r="B12" t="inlineStr">
+      <c r="B13" t="inlineStr">
         <is>
           <t>228</t>
         </is>
       </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr">
+      <c r="C13" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
         <is>
           <t>tiantiananxin</t>
         </is>
       </c>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="13"/>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>总计</t>
-        </is>
-      </c>
-    </row>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="14"/>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>总入款</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>50000</t>
+          <t>总计</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>应下发</t>
+          <t>总入款</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>5952.38</t>
+          <t>50000</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>已下发</t>
+          <t>应下发</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>228</t>
+          <t>5952.38</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
+          <t>已下发</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>5952</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
           <t>未下发</t>
         </is>
       </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>5724.38</t>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>0.38</t>
         </is>
       </c>
     </row>

--- a/bills/JXZFSP01/-1003733706693/6d85008f7f7972fd90832a1022876df384976a1165aef80c1e3f256d2e720bdf/bill-current.xlsx
+++ b/bills/JXZFSP01/-1003733706693/6d85008f7f7972fd90832a1022876df384976a1165aef80c1e3f256d2e720bdf/bill-current.xlsx
@@ -75,7 +75,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>10/23 10:37:09</t>
+          <t>10/27 10:13:36</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -105,7 +105,7 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>xinhui9</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -199,113 +199,59 @@
         </is>
       </c>
     </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>10/23 13:39:54</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>5724</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>jxxiaomei521</t>
-        </is>
-      </c>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
+    <row r="12"/>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>10/23 10:38:04</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>228</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="D13" t="inlineStr">
-        <is>
-          <t>tiantiananxin</t>
-        </is>
-      </c>
-      <c r="E13" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="14"/>
+          <t>总计</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>总入款</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>50000</t>
+        </is>
+      </c>
+    </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>总计</t>
+          <t>应下发</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>5952.38</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>总入款</t>
+          <t>已下发</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>50000</t>
+          <t>0</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>应下发</t>
+          <t>未下发</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
           <t>5952.38</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>已下发</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>5952</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>未下发</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>0.38</t>
         </is>
       </c>
     </row>

--- a/bills/JXZFSP01/-1003733706693/6d85008f7f7972fd90832a1022876df384976a1165aef80c1e3f256d2e720bdf/bill-current.xlsx
+++ b/bills/JXZFSP01/-1003733706693/6d85008f7f7972fd90832a1022876df384976a1165aef80c1e3f256d2e720bdf/bill-current.xlsx
@@ -199,59 +199,86 @@
         </is>
       </c>
     </row>
-    <row r="12"/>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>总计</t>
-        </is>
-      </c>
-    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>10/27 10:13:41</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>238</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>xinhui9</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="13"/>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>总入款</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>50000</t>
+          <t>总计</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>应下发</t>
+          <t>总入款</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>5952.38</t>
+          <t>50000</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>已下发</t>
+          <t>应下发</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>5952.38</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
+          <t>已下发</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>238</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
           <t>未下发</t>
         </is>
       </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>5952.38</t>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>5714.38</t>
         </is>
       </c>
     </row>

--- a/bills/JXZFSP01/-1003733706693/6d85008f7f7972fd90832a1022876df384976a1165aef80c1e3f256d2e720bdf/bill-current.xlsx
+++ b/bills/JXZFSP01/-1003733706693/6d85008f7f7972fd90832a1022876df384976a1165aef80c1e3f256d2e720bdf/bill-current.xlsx
@@ -202,83 +202,110 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
+          <t>10/27 11:57:45</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>5714</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>jxxiaomei521</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
           <t>10/27 10:13:41</t>
         </is>
       </c>
-      <c r="B12" t="inlineStr">
+      <c r="B13" t="inlineStr">
         <is>
           <t>238</t>
         </is>
       </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr">
+      <c r="C13" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
         <is>
           <t>xinhui9</t>
         </is>
       </c>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="13"/>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>总计</t>
-        </is>
-      </c>
-    </row>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="14"/>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>总入款</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>50000</t>
+          <t>总计</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>应下发</t>
+          <t>总入款</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>5952.38</t>
+          <t>50000</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>已下发</t>
+          <t>应下发</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>238</t>
+          <t>5952.38</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
+          <t>已下发</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>5952</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
           <t>未下发</t>
         </is>
       </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>5714.38</t>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>0.38</t>
         </is>
       </c>
     </row>

--- a/bills/JXZFSP01/-1003733706693/6d85008f7f7972fd90832a1022876df384976a1165aef80c1e3f256d2e720bdf/bill-current.xlsx
+++ b/bills/JXZFSP01/-1003733706693/6d85008f7f7972fd90832a1022876df384976a1165aef80c1e3f256d2e720bdf/bill-current.xlsx
@@ -75,12 +75,12 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>10/27 10:13:36</t>
+          <t>10/30 09:54:02</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>50000</t>
+          <t>120000</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -90,12 +90,12 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>8.4</t>
+          <t>8.3</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>5952.38</t>
+          <t>14457.83</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -199,113 +199,59 @@
         </is>
       </c>
     </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>10/27 11:57:45</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>5714</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>jxxiaomei521</t>
-        </is>
-      </c>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
+    <row r="12"/>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>10/27 10:13:41</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>238</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="D13" t="inlineStr">
-        <is>
-          <t>xinhui9</t>
-        </is>
-      </c>
-      <c r="E13" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="14"/>
+          <t>总计</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>总入款</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>120000</t>
+        </is>
+      </c>
+    </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>总计</t>
+          <t>应下发</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>14457.83</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>总入款</t>
+          <t>已下发</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>50000</t>
+          <t>0</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>应下发</t>
+          <t>未下发</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>5952.38</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>已下发</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>5952</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>未下发</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>0.38</t>
+          <t>14457.83</t>
         </is>
       </c>
     </row>

--- a/bills/JXZFSP01/-1003733706693/6d85008f7f7972fd90832a1022876df384976a1165aef80c1e3f256d2e720bdf/bill-current.xlsx
+++ b/bills/JXZFSP01/-1003733706693/6d85008f7f7972fd90832a1022876df384976a1165aef80c1e3f256d2e720bdf/bill-current.xlsx
@@ -199,59 +199,86 @@
         </is>
       </c>
     </row>
-    <row r="12"/>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>总计</t>
-        </is>
-      </c>
-    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>10/30 12:44:02</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>14457</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>jxxiaomei521</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="13"/>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>总入款</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>120000</t>
+          <t>总计</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>应下发</t>
+          <t>总入款</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>14457.83</t>
+          <t>120000</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>已下发</t>
+          <t>应下发</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>14457.83</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
+          <t>已下发</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>14457</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
           <t>未下发</t>
         </is>
       </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>14457.83</t>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>0.83</t>
         </is>
       </c>
     </row>
